--- a/tablas_de_variables.xlsx
+++ b/tablas_de_variables.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Documentos\avance_proyecto\avance_proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CA21BF6-C59E-446C-990C-778355A6375A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{99AB2B13-A0CC-45E9-82F4-A2322831F8FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ejercicio 1" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="57">
   <si>
     <t>Nombre</t>
   </si>
@@ -192,16 +192,13 @@
     <t>Combustible que sobra tras cubrir la misión.</t>
   </si>
   <si>
-    <t>Combustible total requerido (</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
     <t>integer</t>
   </si>
   <si>
-    <t>d</t>
+    <t>Entero</t>
+  </si>
+  <si>
+    <t>cadena caracteres</t>
   </si>
 </sst>
 </file>
@@ -636,7 +633,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>5</v>
@@ -650,7 +647,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>8</v>
@@ -664,7 +661,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>10</v>
@@ -678,7 +675,7 @@
         <v>11</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>51</v>
@@ -692,7 +689,7 @@
         <v>13</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>50</v>
@@ -706,7 +703,7 @@
         <v>14</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>49</v>
@@ -720,7 +717,7 @@
         <v>15</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>48</v>
@@ -734,7 +731,7 @@
         <v>16</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>47</v>
@@ -748,7 +745,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>46</v>
@@ -762,7 +759,7 @@
         <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>45</v>
@@ -806,7 +803,7 @@
         <v>19</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>20</v>
@@ -820,7 +817,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>21</v>
@@ -834,7 +831,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>22</v>
@@ -848,7 +845,7 @@
         <v>23</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>52</v>
@@ -862,7 +859,7 @@
         <v>24</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>48</v>
@@ -876,7 +873,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>53</v>
@@ -920,7 +917,7 @@
         <v>26</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>27</v>
@@ -934,7 +931,7 @@
         <v>28</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>29</v>
@@ -948,7 +945,7 @@
         <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>31</v>
@@ -962,7 +959,7 @@
         <v>32</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>33</v>
@@ -1006,7 +1003,7 @@
         <v>34</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>35</v>
@@ -1020,7 +1017,7 @@
         <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>21</v>
@@ -1034,7 +1031,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>22</v>
@@ -1048,7 +1045,7 @@
         <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>36</v>
@@ -1062,7 +1059,7 @@
         <v>28</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>37</v>
@@ -1076,7 +1073,7 @@
         <v>38</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>39</v>
@@ -1090,7 +1087,7 @@
         <v>40</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>41</v>
@@ -1104,7 +1101,7 @@
         <v>30</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C9" s="3" t="s">
         <v>42</v>
@@ -1118,7 +1115,7 @@
         <v>32</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>43</v>
@@ -1132,10 +1129,10 @@
         <v>15</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>44</v>

--- a/tablas_de_variables.xlsx
+++ b/tablas_de_variables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Documentos\avance_proyecto\avance_proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67B11EA1-5662-4706-AFF0-D6739AD9CC7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3FF0A5E1-5A40-4FB2-BEA6-0C4926B2F56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ejercicio 1" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,28 @@
     <sheet name="Ejercicio 3" sheetId="3" r:id="rId3"/>
     <sheet name="Ejercicio 4" sheetId="4" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="74">
   <si>
     <t>Nombre</t>
   </si>
@@ -42,78 +53,162 @@
     <t>Categoría</t>
   </si>
   <si>
+    <t>COMBUSTIBLE_POR_DIA</t>
+  </si>
+  <si>
+    <t>Entero</t>
+  </si>
+  <si>
+    <t>La cantidad de combustible que se necesita por cada dia de viaje</t>
+  </si>
+  <si>
+    <t>Constante</t>
+  </si>
+  <si>
+    <t>RESERVA_COMBUSTIBLE</t>
+  </si>
+  <si>
+    <t>La cantidad de combustible extra que debería haber después del viaje</t>
+  </si>
+  <si>
+    <t>OXIGENO_POR_TRIPULANTE_DIA</t>
+  </si>
+  <si>
+    <t>La cantidad de unidades de oxigeno necesarias para un tripulante por dia</t>
+  </si>
+  <si>
+    <t>RESERVA_OXIGENO</t>
+  </si>
+  <si>
+    <t>Las 5 unidades de oxigeno extras de emergencia</t>
+  </si>
+  <si>
+    <t>ENERGIA_POR_DIA</t>
+  </si>
+  <si>
+    <t>La cantidad de unidades de energia que consume la nave por dia</t>
+  </si>
+  <si>
+    <t>RESERVA_ENERGIA</t>
+  </si>
+  <si>
+    <t>Las 10 unidades de energía para las operaciones de exploración</t>
+  </si>
+  <si>
+    <t>RESERVA_PROVISIONES</t>
+  </si>
+  <si>
+    <t>Las 3 proviciones extras de emergencia</t>
+  </si>
+  <si>
     <t>mision</t>
   </si>
   <si>
+    <t>cadena caracteres</t>
+  </si>
+  <si>
     <t>Nombre de la misión.</t>
   </si>
   <si>
+    <t>Entrada/Salida</t>
+  </si>
+  <si>
+    <t>tripulantes</t>
+  </si>
+  <si>
+    <t>Cantidad de tripulantes de la misión.</t>
+  </si>
+  <si>
+    <t>dias</t>
+  </si>
+  <si>
+    <t>Días estimados para llegar al destino.</t>
+  </si>
+  <si>
+    <t>combustible_ida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combustible necesario para llegar al destino </t>
+  </si>
+  <si>
+    <t>Salida</t>
+  </si>
+  <si>
+    <t>combustible_regreso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combustible necesario para regresar </t>
+  </si>
+  <si>
+    <t>reserva_combustible</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva fija de combustible para emergencias </t>
+  </si>
+  <si>
+    <t>combustible_total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Combustible total requerido </t>
+  </si>
+  <si>
+    <t>oxigeno</t>
+  </si>
+  <si>
+    <t>Oxígeno requerido</t>
+  </si>
+  <si>
+    <t>energia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Energía requerida </t>
+  </si>
+  <si>
+    <t>provisiones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provisiones requeridas </t>
+  </si>
+  <si>
+    <t>Constante/Salida</t>
+  </si>
+  <si>
+    <t>disponible</t>
+  </si>
+  <si>
+    <t>Combustible disponible en la nave.</t>
+  </si>
+  <si>
+    <t>Combustible requerido para llegar al destino.</t>
+  </si>
+  <si>
+    <t>Combustible requerido para regresar.</t>
+  </si>
+  <si>
+    <t>reserva</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reserva de emergencia fija </t>
+  </si>
+  <si>
+    <t>total_requerido</t>
+  </si>
+  <si>
+    <t>adicional</t>
+  </si>
+  <si>
+    <t>Combustible que sobra tras cubrir la misión.</t>
+  </si>
+  <si>
+    <t>oxigeno_disponible</t>
+  </si>
+  <si>
+    <t>Cantidad de oxígeno que posee la nave.</t>
+  </si>
+  <si>
     <t>Entrada</t>
   </si>
   <si>
-    <t>tripulantes</t>
-  </si>
-  <si>
-    <t>Cantidad de tripulantes de la misión.</t>
-  </si>
-  <si>
-    <t>dias</t>
-  </si>
-  <si>
-    <t>Días estimados para llegar al destino.</t>
-  </si>
-  <si>
-    <t>combustible_ida</t>
-  </si>
-  <si>
-    <t>Salida</t>
-  </si>
-  <si>
-    <t>combustible_regreso</t>
-  </si>
-  <si>
-    <t>reserva_combustible</t>
-  </si>
-  <si>
-    <t>combustible_total</t>
-  </si>
-  <si>
-    <t>oxigeno</t>
-  </si>
-  <si>
-    <t>energia</t>
-  </si>
-  <si>
-    <t>provisiones</t>
-  </si>
-  <si>
-    <t>disponible</t>
-  </si>
-  <si>
-    <t>Combustible disponible en la nave.</t>
-  </si>
-  <si>
-    <t>Combustible requerido para llegar al destino.</t>
-  </si>
-  <si>
-    <t>Combustible requerido para regresar.</t>
-  </si>
-  <si>
-    <t>reserva</t>
-  </si>
-  <si>
-    <t>total_requerido</t>
-  </si>
-  <si>
-    <t>adicional</t>
-  </si>
-  <si>
-    <t>oxigeno_disponible</t>
-  </si>
-  <si>
-    <t>Cantidad de oxígeno que posee la nave.</t>
-  </si>
-  <si>
     <t>oxigeno_requerido</t>
   </si>
   <si>
@@ -156,6 +251,9 @@
     <t>Energía que necesita la misión.</t>
   </si>
   <si>
+    <t>integer</t>
+  </si>
+  <si>
     <t>Provisiones que posee la nave.</t>
   </si>
   <si>
@@ -163,46 +261,13 @@
   </si>
   <si>
     <t>Intermedia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Provisiones requeridas </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Energía requerida </t>
-  </si>
-  <si>
-    <t>Oxígeno requerido</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combustible total requerido </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva fija de combustible para emergencias </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combustible necesario para regresar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Combustible necesario para llegar al destino </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reserva de emergencia fija </t>
-  </si>
-  <si>
-    <t>Combustible que sobra tras cubrir la misión.</t>
-  </si>
-  <si>
-    <t>cadena caracteres</t>
-  </si>
-  <si>
-    <t>int</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -224,8 +289,14 @@
       <sz val="11"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -239,17 +310,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC00000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF79646"/>
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -294,10 +356,8 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -602,16 +662,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D21"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
-    <col min="2" max="2" width="18.44140625" customWidth="1"/>
+    <col min="1" max="1" width="36.7109375" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
     <col min="3" max="3" width="72" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -625,146 +685,247 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="15">
       <c r="A3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:4" ht="15">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+        <v>13</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15">
       <c r="A6" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15">
       <c r="A8" s="2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+        <v>19</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
+        <v>27</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="15"/>
+    <row r="20" spans="1:4" ht="15"/>
+    <row r="21" spans="1:4" ht="15"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -772,16 +933,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="72" customWidth="1"/>
-    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="4" max="4" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -795,93 +956,105 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="15">
       <c r="A2" s="2" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+        <v>5</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+        <v>45</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+        <v>46</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="3"/>
-    </row>
+      <c r="D8" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -890,7 +1063,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
@@ -898,7 +1071,7 @@
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -912,60 +1085,60 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5" s="2" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D5" s="4" t="s">
         <v>55</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -975,16 +1148,16 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D13"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="1" max="1" width="31.85546875" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
     <col min="3" max="3" width="72" customWidth="1"/>
     <col min="4" max="4" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" ht="24" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -998,146 +1171,161 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D2" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C5" s="3" t="s">
+      <c r="B12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>44</v>
-      </c>
-    </row>
+      <c r="D12" s="4" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
